--- a/results/log_pv_inst_fit/log_pv_inst_fit_capacities_effects.xlsx
+++ b/results/log_pv_inst_fit/log_pv_inst_fit_capacities_effects.xlsx
@@ -511,298 +511,298 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_gdp_cap</t>
+          <t>Households per capita</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-3.920</t>
+          <t>-5.931</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.091</t>
+          <t>-0.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-3.829</t>
+          <t>-5.930</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.705</t>
+          <t>-1.942</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.083</t>
+          <t>-0.060</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.622</t>
+          <t>-1.881</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.087</t>
+          <t>-0.713</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.106</t>
+          <t>-0.051</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-0.663</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-2.027</t>
+          <t>-0.128</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.077</t>
+          <t>-0.005</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-1.950</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-0.180</t>
+          <t>-0.228</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.141</t>
+          <t>-0.179</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.211</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.037</t>
+          <t>-0.066</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.082</t>
+          <t>-0.145</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_fcapacity</t>
+          <t>GDP per capita</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.981</t>
+          <t>-3.920</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>-0.091</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.207</t>
+          <t>-3.829</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-8.723</t>
+          <t>-0.705</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>-0.083</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.224</t>
+          <t>-0.622</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-8.330</t>
+          <t>-0.087</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>-0.106</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.488</t>
+          <t>0.019</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23.132</t>
+          <t>-2.027</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.878</t>
+          <t>-0.077</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>22.254</t>
+          <t>-1.950</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>5.530</t>
+          <t>-0.180</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>4.327</t>
+          <t>-0.141</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4.086</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>-0.037</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2.814</t>
+          <t>-0.082</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hcapacity</t>
+          <t>Firms per capita</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-5.931</t>
+          <t>15.981</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.000</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.930</t>
+          <t>15.207</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.942</t>
+          <t>-8.723</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.060</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.881</t>
+          <t>-9.224</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.713</t>
+          <t>-8.330</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.051</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.663</t>
+          <t>-8.488</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.128</t>
+          <t>23.132</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.005</t>
+          <t>0.878</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.123</t>
+          <t>22.254</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.228</t>
+          <t>5.530</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>1.202</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.179</t>
+          <t>4.327</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.211</t>
+          <t>4.086</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>1.272</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.145</t>
+          <t>2.814</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_acapacity</t>
+          <t>Firm assets per capita</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
